--- a/test-data/DSAlgo Data.xlsx
+++ b/test-data/DSAlgo Data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="64">
   <si>
     <t>ExpectedMessage</t>
   </si>
@@ -61,6 +61,9 @@
     <t>username1</t>
   </si>
   <si>
+    <t>pythoncode</t>
+  </si>
+  <si>
     <t>Test@1234</t>
   </si>
   <si>
@@ -70,10 +73,24 @@
     <t>viji #12</t>
   </si>
   <si>
+    <t>num1 = 10
+num2 = 15
+# Add two numbers
+sum = num1 + num2
+# Display the sum
+print('The sum of {0} and {1} is {2}'.format(num1, num2, sum))</t>
+  </si>
+  <si>
     <t>viji@123</t>
   </si>
   <si>
     <t>vijayarani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a = 5
+b = 10
+print(a + b)'
+   </t>
   </si>
   <si>
     <t>TestType</t>
@@ -242,7 +259,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -252,7 +269,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -264,6 +280,11 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -280,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -288,8 +309,14 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,6 +546,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="6" width="11.22"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -1579,6 +1609,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="6" width="11.22"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
@@ -1590,27 +1623,36 @@
       <c r="C1" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>17</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
+      <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2607,6 +2649,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="6" width="11.22"/>
+  </cols>
   <sheetData>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3602,28 +3647,31 @@
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="6" width="11.22"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -3634,346 +3682,346 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
